--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6792BF37-2CC8-4A1A-82AA-B353A00638E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA385F66-1F8A-4D67-AB58-F2F5F2384F4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="59">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -208,6 +208,12 @@
   </si>
   <si>
     <t>AUGUST</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>High</t>
   </si>
 </sst>
 </file>
@@ -1033,25 +1039,47 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="15" t="str">
+      <c r="A7" s="13">
+        <v>46256</v>
+      </c>
+      <c r="B7" s="14">
+        <v>540</v>
+      </c>
+      <c r="C7" s="14">
+        <v>60</v>
+      </c>
+      <c r="D7" s="14">
+        <v>120</v>
+      </c>
+      <c r="E7" s="14">
+        <v>120</v>
+      </c>
+      <c r="F7" s="14">
+        <v>0</v>
+      </c>
+      <c r="G7" s="14">
+        <v>0</v>
+      </c>
+      <c r="H7" s="14">
+        <v>120</v>
+      </c>
+      <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J7" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
+        <v>480</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N7" s="17"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\CAP776\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA385F66-1F8A-4D67-AB58-F2F5F2384F4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02FD9A5E-0A02-4872-814F-614570893AC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="58">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -211,9 +211,6 @@
   </si>
   <si>
     <t>Excellent</t>
-  </si>
-  <si>
-    <t>High</t>
   </si>
 </sst>
 </file>
@@ -1052,7 +1049,7 @@
         <v>120</v>
       </c>
       <c r="E7" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="F7" s="14">
         <v>0</v>
@@ -1065,11 +1062,11 @@
       </c>
       <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v>960</v>
+        <v>900</v>
       </c>
       <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>540</v>
       </c>
       <c r="K7" s="16" t="s">
         <v>57</v>
@@ -1078,7 +1075,7 @@
         <v>50</v>
       </c>
       <c r="M7" s="16" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="N7" s="17"/>
     </row>

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A4EFA1C-13F0-42BB-8ED4-4E0D97BA0DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB174402-A966-4377-A028-F33BB0C037B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1179,25 +1179,47 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="A10" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B10" s="14">
+        <v>420</v>
+      </c>
+      <c r="C10" s="14">
+        <v>30</v>
+      </c>
+      <c r="D10" s="14">
+        <v>120</v>
+      </c>
+      <c r="E10" s="14">
+        <v>60</v>
+      </c>
+      <c r="F10" s="14">
+        <v>300</v>
+      </c>
+      <c r="G10" s="14">
+        <v>6</v>
+      </c>
+      <c r="H10" s="14">
+        <v>120</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
+        <v>390</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N10" s="17"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB174402-A966-4377-A028-F33BB0C037B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC1AA209-63B1-4D71-AA35-B6AB7BA062E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -220,6 +220,15 @@
   </si>
   <si>
     <t>great day</t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>but happy day</t>
   </si>
 </sst>
 </file>
@@ -1223,26 +1232,50 @@
       <c r="N10" s="17"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="A11" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B11" s="14">
+        <v>500</v>
+      </c>
+      <c r="C11" s="14">
+        <v>30</v>
+      </c>
+      <c r="D11" s="14">
+        <v>120</v>
+      </c>
+      <c r="E11" s="14">
+        <v>30</v>
+      </c>
+      <c r="F11" s="14">
+        <v>300</v>
+      </c>
+      <c r="G11" s="14">
+        <v>6</v>
+      </c>
+      <c r="H11" s="14">
+        <v>120</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+        <v>340</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="13"/>

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC1AA209-63B1-4D71-AA35-B6AB7BA062E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57390BCB-0FB8-465D-9717-EEB40CCD17E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1278,25 +1278,47 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="A12" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B12" s="14">
+        <v>420</v>
+      </c>
+      <c r="C12" s="14">
+        <v>30</v>
+      </c>
+      <c r="D12" s="14">
+        <v>100</v>
+      </c>
+      <c r="E12" s="14">
+        <v>30</v>
+      </c>
+      <c r="F12" s="14">
+        <v>250</v>
+      </c>
+      <c r="G12" s="14">
+        <v>5</v>
+      </c>
+      <c r="H12" s="14">
+        <v>140</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>970</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
+        <v>470</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N12" s="17"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57390BCB-0FB8-465D-9717-EEB40CCD17E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25AD89D2-C765-4B60-AA0D-FB3972A81ABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -229,6 +229,9 @@
   </si>
   <si>
     <t>but happy day</t>
+  </si>
+  <si>
+    <t>mentor meeting</t>
   </si>
 </sst>
 </file>
@@ -1322,26 +1325,50 @@
       <c r="N12" s="17"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B13" s="14">
+        <v>420</v>
+      </c>
+      <c r="C13" s="14">
+        <v>60</v>
+      </c>
+      <c r="D13" s="14">
+        <v>200</v>
+      </c>
+      <c r="E13" s="14">
+        <v>60</v>
+      </c>
+      <c r="F13" s="14">
+        <v>200</v>
+      </c>
+      <c r="G13" s="14">
+        <v>4</v>
+      </c>
+      <c r="H13" s="14">
+        <v>420</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>1360</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>80</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25AD89D2-C765-4B60-AA0D-FB3972A81ABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{500B2B66-6095-4423-8FDC-852ED3EA7912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1371,25 +1371,47 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B14" s="14">
+        <v>500</v>
+      </c>
+      <c r="C14" s="14">
+        <v>60</v>
+      </c>
+      <c r="D14" s="14">
+        <v>180</v>
+      </c>
+      <c r="E14" s="14">
+        <v>30</v>
+      </c>
+      <c r="F14" s="14">
+        <v>0</v>
+      </c>
+      <c r="G14" s="14">
+        <v>0</v>
+      </c>
+      <c r="H14" s="14">
+        <v>420</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
+        <v>250</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N14" s="17"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{500B2B66-6095-4423-8FDC-852ED3EA7912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AE01600-140B-4931-B222-AA31D4FE27BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -232,6 +232,9 @@
   </si>
   <si>
     <t>mentor meeting</t>
+  </si>
+  <si>
+    <t>Sunday</t>
   </si>
 </sst>
 </file>
@@ -1415,26 +1418,50 @@
       <c r="N14" s="17"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B15" s="14">
+        <v>420</v>
+      </c>
+      <c r="C15" s="14">
+        <v>60</v>
+      </c>
+      <c r="D15" s="14">
+        <v>120</v>
+      </c>
+      <c r="E15" s="14">
+        <v>60</v>
+      </c>
+      <c r="F15" s="14">
+        <v>0</v>
+      </c>
+      <c r="G15" s="14">
+        <v>0</v>
+      </c>
+      <c r="H15" s="14">
+        <v>600</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>1260</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>180</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AE01600-140B-4931-B222-AA31D4FE27BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31CE396B-719E-4542-AB00-29A0EFF22AD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1464,25 +1464,47 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B16" s="14">
+        <v>420</v>
+      </c>
+      <c r="C16" s="14">
+        <v>30</v>
+      </c>
+      <c r="D16" s="14">
+        <v>120</v>
+      </c>
+      <c r="E16" s="14">
+        <v>30</v>
+      </c>
+      <c r="F16" s="14">
+        <v>300</v>
+      </c>
+      <c r="G16" s="14">
+        <v>6</v>
+      </c>
+      <c r="H16" s="14">
+        <v>400</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>1300</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
+        <v>140</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N16" s="17"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31CE396B-719E-4542-AB00-29A0EFF22AD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75AEFEA9-5F3C-46BB-B3E6-A44FF9460869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -235,6 +235,9 @@
   </si>
   <si>
     <t>Sunday</t>
+  </si>
+  <si>
+    <t>Monday</t>
   </si>
 </sst>
 </file>
@@ -1505,7 +1508,9 @@
       <c r="M16" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="N16" s="17"/>
+      <c r="N16" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="13"/>

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75AEFEA9-5F3C-46BB-B3E6-A44FF9460869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5509CC13-FC10-451D-A6F1-2235B833111C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1513,25 +1513,47 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B17" s="14">
+        <v>420</v>
+      </c>
+      <c r="C17" s="14">
+        <v>30</v>
+      </c>
+      <c r="D17" s="14">
+        <v>120</v>
+      </c>
+      <c r="E17" s="14">
+        <v>30</v>
+      </c>
+      <c r="F17" s="14">
+        <v>300</v>
+      </c>
+      <c r="G17" s="14">
+        <v>6</v>
+      </c>
+      <c r="H17" s="14">
+        <v>500</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>1400</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
+        <v>40</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N17" s="17"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5509CC13-FC10-451D-A6F1-2235B833111C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D779DA7-6F78-4371-8888-CA11F5A0A7DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -238,6 +238,9 @@
   </si>
   <si>
     <t>Monday</t>
+  </si>
+  <si>
+    <t>English CA</t>
   </si>
 </sst>
 </file>
@@ -1557,48 +1560,94 @@
       <c r="N17" s="17"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B18" s="14">
+        <v>420</v>
+      </c>
+      <c r="C18" s="14">
+        <v>0</v>
+      </c>
+      <c r="D18" s="14">
+        <v>120</v>
+      </c>
+      <c r="E18" s="14">
+        <v>60</v>
+      </c>
+      <c r="F18" s="14">
+        <v>300</v>
+      </c>
+      <c r="G18" s="14">
+        <v>6</v>
+      </c>
+      <c r="H18" s="14">
+        <v>400</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>1300</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
+        <v>140</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N18" s="17"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B19" s="14">
+        <v>400</v>
+      </c>
+      <c r="C19" s="14">
+        <v>30</v>
+      </c>
+      <c r="D19" s="14">
+        <v>140</v>
+      </c>
+      <c r="E19" s="14">
+        <v>30</v>
+      </c>
+      <c r="F19" s="14">
+        <v>200</v>
+      </c>
+      <c r="G19" s="14">
+        <v>4</v>
+      </c>
+      <c r="H19" s="14">
+        <v>350</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>290</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="13"/>

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D779DA7-6F78-4371-8888-CA11F5A0A7DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA92C1ED-C310-4DA4-BE3C-FE702BB6DA7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -241,6 +241,9 @@
   </si>
   <si>
     <t>English CA</t>
+  </si>
+  <si>
+    <t>ca database</t>
   </si>
 </sst>
 </file>
@@ -1650,26 +1653,50 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B20" s="14">
+        <v>420</v>
+      </c>
+      <c r="C20" s="14">
+        <v>0</v>
+      </c>
+      <c r="D20" s="14">
+        <v>60</v>
+      </c>
+      <c r="E20" s="14">
+        <v>30</v>
+      </c>
+      <c r="F20" s="14">
+        <v>250</v>
+      </c>
+      <c r="G20" s="14">
+        <v>5</v>
+      </c>
+      <c r="H20" s="14">
+        <v>490</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>1250</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>190</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA92C1ED-C310-4DA4-BE3C-FE702BB6DA7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B63EB9FF-566A-480C-A125-73A12CD4FA44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1699,25 +1699,47 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B21" s="14">
+        <v>420</v>
+      </c>
+      <c r="C21" s="14">
+        <v>30</v>
+      </c>
+      <c r="D21" s="14">
+        <v>200</v>
+      </c>
+      <c r="E21" s="14">
+        <v>60</v>
+      </c>
+      <c r="F21" s="14">
+        <v>0</v>
+      </c>
+      <c r="G21" s="14">
+        <v>0</v>
+      </c>
+      <c r="H21" s="14">
+        <v>450</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
+        <v>280</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N21" s="17"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B63EB9FF-566A-480C-A125-73A12CD4FA44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22704D6A-0CF1-48FF-9033-43E51689484E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1743,47 +1743,91 @@
       <c r="N21" s="17"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B22" s="14">
+        <v>420</v>
+      </c>
+      <c r="C22" s="14">
+        <v>30</v>
+      </c>
+      <c r="D22" s="14">
+        <v>120</v>
+      </c>
+      <c r="E22" s="14">
+        <v>60</v>
+      </c>
+      <c r="F22" s="14">
+        <v>0</v>
+      </c>
+      <c r="G22" s="14">
+        <v>0</v>
+      </c>
+      <c r="H22" s="14">
+        <v>450</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
+        <v>360</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N22" s="17"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B23" s="14">
+        <v>420</v>
+      </c>
+      <c r="C23" s="14">
+        <v>30</v>
+      </c>
+      <c r="D23" s="14">
+        <v>120</v>
+      </c>
+      <c r="E23" s="14">
+        <v>60</v>
+      </c>
+      <c r="F23" s="14">
+        <v>300</v>
+      </c>
+      <c r="G23" s="14">
+        <v>6</v>
+      </c>
+      <c r="H23" s="14">
+        <v>500</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>1430</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
+        <v>10</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N23" s="17"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628847.xlsx
+++ b/12628847.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tarun\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22704D6A-0CF1-48FF-9033-43E51689484E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B426F96-A680-4D4E-963F-46BEFC0D25B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1831,25 +1831,47 @@
       <c r="N23" s="17"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B24" s="14">
+        <v>420</v>
+      </c>
+      <c r="C24" s="14">
+        <v>0</v>
+      </c>
+      <c r="D24" s="14">
+        <v>120</v>
+      </c>
+      <c r="E24" s="14">
+        <v>0</v>
+      </c>
+      <c r="F24" s="14">
+        <v>300</v>
+      </c>
+      <c r="G24" s="14">
+        <v>6</v>
+      </c>
+      <c r="H24" s="14">
+        <v>400</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>1240</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
+        <v>200</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N24" s="17"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
